--- a/6.4 Bonaire with disturbances/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/6.4 Bonaire with disturbances/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>58.03072108626378</v>
+        <v>56.81371733109724</v>
       </c>
       <c r="C3" t="n">
-        <v>49.44738775293044</v>
+        <v>48.23038399776391</v>
       </c>
       <c r="D3" t="n">
-        <v>6.008628516649134</v>
+        <v>5.98393944499537</v>
       </c>
       <c r="E3" t="n">
-        <v>5.45522156558385</v>
+        <v>4.406571686883812</v>
       </c>
       <c r="F3" t="n">
-        <v>3.004314258324567</v>
+        <v>3.004406809585668</v>
       </c>
       <c r="G3" t="n">
-        <v>35.05033301378662</v>
+        <v>34.90631342913966</v>
       </c>
       <c r="H3" t="n">
-        <v>3.004314258324567</v>
+        <v>3.004406809585668</v>
       </c>
       <c r="I3" t="n">
-        <v>2.503595215270473</v>
+        <v>2.50367234132139</v>
       </c>
       <c r="J3" t="n">
-        <v>3.004314258324567</v>
+        <v>3.004406809585668</v>
       </c>
       <c r="K3" t="n">
-        <v>41.96927891373623</v>
+        <v>43.18628266890276</v>
       </c>
       <c r="L3" t="n">
         <v>8.5</v>
       </c>
       <c r="M3" t="n">
-        <v>99.91666666666666</v>
+        <v>99.91666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>58.3340580180969</v>
+        <v>56.01329847996126</v>
       </c>
       <c r="C4" t="n">
-        <v>50.16955584385376</v>
+        <v>47.84854478909649</v>
       </c>
       <c r="D4" t="n">
-        <v>6.006882496901938</v>
+        <v>5.882455355045811</v>
       </c>
       <c r="E4" t="n">
-        <v>6.174507450754535</v>
+        <v>4.703107693001797</v>
       </c>
       <c r="F4" t="n">
-        <v>3.007900196890588</v>
+        <v>3.008141736761439</v>
       </c>
       <c r="G4" t="n">
-        <v>35.04014789859464</v>
+        <v>34.31432290443389</v>
       </c>
       <c r="H4" t="n">
-        <v>3.007900196890588</v>
+        <v>3.008141736761439</v>
       </c>
       <c r="I4" t="n">
-        <v>2.08881958117402</v>
+        <v>2.088987317195444</v>
       </c>
       <c r="J4" t="n">
-        <v>3.007900196890588</v>
+        <v>3.008141736761439</v>
       </c>
       <c r="K4" t="n">
-        <v>41.6659419819031</v>
+        <v>43.98670152003874</v>
       </c>
       <c r="L4" t="n">
-        <v>8.094957862707862</v>
+        <v>8.09520723693916</v>
       </c>
       <c r="M4" t="n">
-        <v>99.93045568846472</v>
+        <v>99.9304535460744</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.82610996746541</v>
+        <v>55.53760035881339</v>
       </c>
       <c r="C5" t="n">
-        <v>51.01160382322882</v>
+        <v>47.72246669548331</v>
       </c>
       <c r="D5" t="n">
-        <v>5.998929359293159</v>
+        <v>5.824904941676272</v>
       </c>
       <c r="E5" t="n">
-        <v>7.058414572077747</v>
+        <v>4.957575649846496</v>
       </c>
       <c r="F5" t="n">
-        <v>3.010869949659808</v>
+        <v>3.01128802486762</v>
       </c>
       <c r="G5" t="n">
-        <v>34.99375459587677</v>
+        <v>33.97861215977826</v>
       </c>
       <c r="H5" t="n">
-        <v>3.010869949659808</v>
+        <v>3.01128802486762</v>
       </c>
       <c r="I5" t="n">
-        <v>1.742401591238315</v>
+        <v>1.742643532909502</v>
       </c>
       <c r="J5" t="n">
-        <v>3.010869949659808</v>
+        <v>3.01128802486762</v>
       </c>
       <c r="K5" t="n">
-        <v>41.17389003253459</v>
+        <v>44.46239964118662</v>
       </c>
       <c r="L5" t="n">
-        <v>7.756483378092859</v>
+        <v>7.757106237852414</v>
       </c>
       <c r="M5" t="n">
-        <v>99.94197723385628</v>
+        <v>99.94197257452234</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.46383524712129</v>
+        <v>54.28202280669501</v>
       </c>
       <c r="C6" t="n">
-        <v>50.94169397756868</v>
+        <v>46.75883704806549</v>
       </c>
       <c r="D6" t="n">
-        <v>5.953796399758157</v>
+        <v>5.664954562247394</v>
       </c>
       <c r="E6" t="n">
-        <v>7.286261660774621</v>
+        <v>5.076073500361413</v>
       </c>
       <c r="F6" t="n">
-        <v>3.01336460262509</v>
+        <v>3.013975780577314</v>
       </c>
       <c r="G6" t="n">
-        <v>34.73047899858926</v>
+        <v>33.04556827977648</v>
       </c>
       <c r="H6" t="n">
-        <v>3.01336460262509</v>
+        <v>3.013975780577314</v>
       </c>
       <c r="I6" t="n">
-        <v>1.453204380123982</v>
+        <v>1.453499122577794</v>
       </c>
       <c r="J6" t="n">
-        <v>3.01336460262509</v>
+        <v>3.013975780577314</v>
       </c>
       <c r="K6" t="n">
-        <v>41.53616475287871</v>
+        <v>45.71797719330499</v>
       </c>
       <c r="L6" t="n">
-        <v>7.473741225351544</v>
+        <v>7.474778993826492</v>
       </c>
       <c r="M6" t="n">
-        <v>99.95159995579894</v>
+        <v>99.95159323519698</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>70.1281073484792</v>
+        <v>66.87815085046107</v>
       </c>
       <c r="C7" t="n">
-        <v>59.07014821192172</v>
+        <v>55.48058854627837</v>
       </c>
       <c r="D7" t="n">
-        <v>5.967607255429446</v>
+        <v>5.679664795475241</v>
       </c>
       <c r="E7" t="n">
-        <v>12.97762308848196</v>
+        <v>11.18039689942113</v>
       </c>
       <c r="F7" t="n">
-        <v>3.020354620559448</v>
+        <v>3.021802195809457</v>
       </c>
       <c r="G7" t="n">
-        <v>37.24158662491632</v>
+        <v>35.7427915475778</v>
       </c>
       <c r="H7" t="n">
-        <v>3.020354620559448</v>
+        <v>3.021802195809457</v>
       </c>
       <c r="I7" t="n">
-        <v>4.88022651797314</v>
+        <v>5.209891020558521</v>
       </c>
       <c r="J7" t="n">
-        <v>3.020354620559448</v>
+        <v>3.021802195809457</v>
       </c>
       <c r="K7" t="n">
-        <v>29.8718926515208</v>
+        <v>33.12184914953893</v>
       </c>
       <c r="L7" t="n">
-        <v>10.89566139683788</v>
+        <v>11.2243490544076</v>
       </c>
       <c r="M7" t="n">
-        <v>99.83770226028039</v>
+        <v>99.82678675022491</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68.77614258496092</v>
+        <v>65.05175107703715</v>
       </c>
       <c r="C8" t="n">
-        <v>58.53301606447627</v>
+        <v>54.52185163993728</v>
       </c>
       <c r="D8" t="n">
-        <v>5.83551709694358</v>
+        <v>5.494687644350736</v>
       </c>
       <c r="E8" t="n">
-        <v>13.36951743092763</v>
+        <v>11.54147946693607</v>
       </c>
       <c r="F8" t="n">
-        <v>3.026319675760605</v>
+        <v>3.028539721291574</v>
       </c>
       <c r="G8" t="n">
-        <v>36.41726175416101</v>
+        <v>34.57870880822755</v>
       </c>
       <c r="H8" t="n">
-        <v>3.026319675760605</v>
+        <v>3.028539721291574</v>
       </c>
       <c r="I8" t="n">
-        <v>4.074887275646891</v>
+        <v>4.351255993648075</v>
       </c>
       <c r="J8" t="n">
-        <v>3.026319675760605</v>
+        <v>3.028539721291574</v>
       </c>
       <c r="K8" t="n">
-        <v>31.22385741503908</v>
+        <v>34.94824892296285</v>
       </c>
       <c r="L8" t="n">
-        <v>10.10756467276318</v>
+        <v>10.38518024208435</v>
       </c>
       <c r="M8" t="n">
-        <v>99.86443815227852</v>
+        <v>99.85528080498447</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>74.55228465532817</v>
+        <v>71.32050865762623</v>
       </c>
       <c r="C9" t="n">
-        <v>62.88904037801733</v>
+        <v>59.24725143999461</v>
       </c>
       <c r="D9" t="n">
-        <v>5.845119100034359</v>
+        <v>5.50474654044469</v>
       </c>
       <c r="E9" t="n">
-        <v>15.82189568029572</v>
+        <v>14.19514861895546</v>
       </c>
       <c r="F9" t="n">
-        <v>3.031299308310317</v>
+        <v>3.034083942973439</v>
       </c>
       <c r="G9" t="n">
-        <v>38.29420653800857</v>
+        <v>36.62173381617294</v>
       </c>
       <c r="H9" t="n">
-        <v>4.848321611576967</v>
+        <v>5.013807147162487</v>
       </c>
       <c r="I9" t="n">
-        <v>3.680143108791905</v>
+        <v>3.916904648943788</v>
       </c>
       <c r="J9" t="n">
-        <v>3.031299308310317</v>
+        <v>3.034083942973439</v>
       </c>
       <c r="K9" t="n">
-        <v>25.44771534467185</v>
+        <v>28.67949134237375</v>
       </c>
       <c r="L9" t="n">
-        <v>11.5407743574625</v>
+        <v>11.94293230972097</v>
       </c>
       <c r="M9" t="n">
-        <v>99.87753008015167</v>
+        <v>99.86967509208934</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>75.22937641199307</v>
+        <v>72.36391993517681</v>
       </c>
       <c r="C10" t="n">
-        <v>63.81085901476331</v>
+        <v>60.47954382934249</v>
       </c>
       <c r="D10" t="n">
-        <v>5.815876128265654</v>
+        <v>5.486253941710868</v>
       </c>
       <c r="E10" t="n">
-        <v>16.60176054888817</v>
+        <v>15.12335827048537</v>
       </c>
       <c r="F10" t="n">
-        <v>3.035460033551706</v>
+        <v>3.03870641180154</v>
       </c>
       <c r="G10" t="n">
-        <v>38.44534832733486</v>
+        <v>36.92336662639417</v>
       </c>
       <c r="H10" t="n">
-        <v>5.197703022307644</v>
+        <v>5.44610530315168</v>
       </c>
       <c r="I10" t="n">
-        <v>3.097768318093348</v>
+        <v>3.307422969831629</v>
       </c>
       <c r="J10" t="n">
-        <v>3.035460033551706</v>
+        <v>3.03870641180154</v>
       </c>
       <c r="K10" t="n">
-        <v>24.77062358800691</v>
+        <v>27.6360800648232</v>
       </c>
       <c r="L10" t="n">
-        <v>11.31539999101405</v>
+        <v>11.7742963814883</v>
       </c>
       <c r="M10" t="n">
-        <v>99.89688259378427</v>
+        <v>99.88992027565399</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>73.51062088869116</v>
+        <v>70.59738275110917</v>
       </c>
       <c r="C11" t="n">
-        <v>62.60993511447364</v>
+        <v>59.26451236768983</v>
       </c>
       <c r="D11" t="n">
-        <v>5.65826061045675</v>
+        <v>5.324729155936354</v>
       </c>
       <c r="E11" t="n">
-        <v>16.58258760231531</v>
+        <v>15.13806337911812</v>
       </c>
       <c r="F11" t="n">
-        <v>3.039017407578268</v>
+        <v>3.042666026447469</v>
       </c>
       <c r="G11" t="n">
-        <v>37.40344451949643</v>
+        <v>35.83627898011174</v>
       </c>
       <c r="H11" t="n">
-        <v>5.20379441324179</v>
+        <v>5.453201901308672</v>
       </c>
       <c r="I11" t="n">
-        <v>2.584498928024341</v>
+        <v>2.759777281739345</v>
       </c>
       <c r="J11" t="n">
-        <v>3.039017407578268</v>
+        <v>3.042666026447469</v>
       </c>
       <c r="K11" t="n">
-        <v>26.48937911130884</v>
+        <v>29.40261724889083</v>
       </c>
       <c r="L11" t="n">
-        <v>10.81463665427047</v>
+        <v>11.24099752314624</v>
       </c>
       <c r="M11" t="n">
-        <v>99.91395088005297</v>
+        <v>99.9081271397269</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>71.41031893761075</v>
+        <v>68.38150946028483</v>
       </c>
       <c r="C12" t="n">
-        <v>60.94196637321417</v>
+        <v>57.50916665103092</v>
       </c>
       <c r="D12" t="n">
-        <v>5.464505461065396</v>
+        <v>5.120894199923893</v>
       </c>
       <c r="E12" t="n">
-        <v>16.37407143734724</v>
+        <v>14.94229861162383</v>
       </c>
       <c r="F12" t="n">
-        <v>3.042075727429843</v>
+        <v>3.046080897305051</v>
       </c>
       <c r="G12" t="n">
-        <v>36.12264278914961</v>
+        <v>34.46443712005815</v>
       </c>
       <c r="H12" t="n">
-        <v>5.209031259769173</v>
+        <v>5.459322185326513</v>
       </c>
       <c r="I12" t="n">
-        <v>2.155916535419629</v>
+        <v>2.302395548742353</v>
       </c>
       <c r="J12" t="n">
-        <v>3.042075727429843</v>
+        <v>3.046080897305051</v>
       </c>
       <c r="K12" t="n">
-        <v>28.58968106238926</v>
+        <v>31.61849053971518</v>
       </c>
       <c r="L12" t="n">
-        <v>10.39656092750701</v>
+        <v>10.7956823292056</v>
       </c>
       <c r="M12" t="n">
-        <v>99.92820836311044</v>
+        <v>99.9233395199517</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>68.36967940044865</v>
+        <v>65.1892389902018</v>
       </c>
       <c r="C13" t="n">
-        <v>58.26208872997162</v>
+        <v>54.70121751837546</v>
       </c>
       <c r="D13" t="n">
-        <v>5.182377438011574</v>
+        <v>4.825830603692425</v>
       </c>
       <c r="E13" t="n">
-        <v>15.82838665728833</v>
+        <v>14.40142134977162</v>
       </c>
       <c r="F13" t="n">
-        <v>3.044742687389045</v>
+        <v>3.049072261162132</v>
       </c>
       <c r="G13" t="n">
-        <v>34.25765978744991</v>
+        <v>32.47861191810635</v>
       </c>
       <c r="H13" t="n">
-        <v>5.213597969818752</v>
+        <v>5.464683441189346</v>
       </c>
       <c r="I13" t="n">
-        <v>1.798172173101999</v>
+        <v>1.9205471551178</v>
       </c>
       <c r="J13" t="n">
-        <v>3.044742687389045</v>
+        <v>3.049072261162132</v>
       </c>
       <c r="K13" t="n">
-        <v>31.63032059955135</v>
+        <v>34.81076100979819</v>
       </c>
       <c r="L13" t="n">
-        <v>10.04770410004871</v>
+        <v>10.42406603991686</v>
       </c>
       <c r="M13" t="n">
-        <v>99.94011342957168</v>
+        <v>99.93604456809052</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>65.64664506308745</v>
+        <v>62.32910358594255</v>
       </c>
       <c r="C14" t="n">
-        <v>55.8398783679307</v>
+        <v>52.16154338890627</v>
       </c>
       <c r="D14" t="n">
-        <v>4.930797283034295</v>
+        <v>4.562792771116515</v>
       </c>
       <c r="E14" t="n">
-        <v>15.30992891785582</v>
+        <v>13.88342533166109</v>
       </c>
       <c r="F14" t="n">
-        <v>3.047061135624948</v>
+        <v>3.051684249233868</v>
       </c>
       <c r="G14" t="n">
-        <v>32.59461083712251</v>
+        <v>30.70832522849977</v>
       </c>
       <c r="H14" t="n">
-        <v>5.217567913507557</v>
+        <v>5.469364762831346</v>
       </c>
       <c r="I14" t="n">
-        <v>1.49961784031737</v>
+        <v>1.60182699336608</v>
       </c>
       <c r="J14" t="n">
-        <v>3.047061135624948</v>
+        <v>3.051684249233868</v>
       </c>
       <c r="K14" t="n">
-        <v>34.35335493691256</v>
+        <v>37.67089641405747</v>
       </c>
       <c r="L14" t="n">
-        <v>9.75681746812613</v>
+        <v>10.11421166494964</v>
       </c>
       <c r="M14" t="n">
-        <v>99.95005077296938</v>
+        <v>99.94665146791338</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>62.22405658158812</v>
+        <v>58.72390021397627</v>
       </c>
       <c r="C15" t="n">
-        <v>52.66808994773788</v>
+        <v>48.82350017984583</v>
       </c>
       <c r="D15" t="n">
-        <v>4.614477308509448</v>
+        <v>4.231344229908138</v>
       </c>
       <c r="E15" t="n">
-        <v>14.53618779491411</v>
+        <v>13.09755585119598</v>
       </c>
       <c r="F15" t="n">
-        <v>3.049102364869048</v>
+        <v>3.053998268666149</v>
       </c>
       <c r="G15" t="n">
-        <v>30.50360488457173</v>
+        <v>28.47762352660152</v>
       </c>
       <c r="H15" t="n">
-        <v>5.221063167371554</v>
+        <v>5.473512051774036</v>
       </c>
       <c r="I15" t="n">
-        <v>1.250518696483176</v>
+        <v>1.335868017164307</v>
       </c>
       <c r="J15" t="n">
-        <v>3.049102364869048</v>
+        <v>3.053998268666149</v>
       </c>
       <c r="K15" t="n">
-        <v>37.77594341841188</v>
+        <v>41.27609978602373</v>
       </c>
       <c r="L15" t="n">
-        <v>9.514310582730314</v>
+        <v>9.855904839870281</v>
       </c>
       <c r="M15" t="n">
-        <v>99.95834394888007</v>
+        <v>99.95550480573985</v>
       </c>
     </row>
   </sheetData>
